--- a/study_case_model/scenario_variables/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios144.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.73597067111876</v>
+        <v>27.51551466689234</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.07684342895796</v>
+        <v>27.81145630025179</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.94571069720234</v>
+        <v>21.58083915597023</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.11321414091531</v>
+        <v>28.94008052266105</v>
       </c>
     </row>
     <row r="6">
@@ -523,11 +523,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.61191737800612</v>
+        <v>28.00720489645503</v>
       </c>
     </row>
     <row r="7">
@@ -535,15 +535,15 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.33703221551266</v>
+        <v>25.01447174704114</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.20328260480533</v>
+        <v>27.70400346885862</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33.31561459992287</v>
+        <v>28.57423408461178</v>
       </c>
     </row>
     <row r="10">
@@ -587,11 +587,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.9951314075263</v>
+        <v>21.33059991720743</v>
       </c>
     </row>
     <row r="11">
@@ -603,11 +603,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33.11339565633956</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="12">
@@ -615,15 +615,15 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33.37311531494515</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="13">
@@ -631,15 +631,15 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.42225238976503</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="14">
@@ -651,11 +651,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>34.1754403122863</v>
+        <v>27.28989434103833</v>
       </c>
     </row>
     <row r="15">
@@ -667,11 +667,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27.92168019192328</v>
+        <v>28.25802211203591</v>
       </c>
     </row>
     <row r="16">
@@ -683,11 +683,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32.71368841933858</v>
+        <v>21.27313994834424</v>
       </c>
     </row>
     <row r="17">
@@ -695,15 +695,15 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33.1104638945835</v>
+        <v>28.70443304779572</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.73953846389585</v>
+        <v>28.4272006435972</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33.27774074042268</v>
+        <v>25.19958812039205</v>
       </c>
     </row>
     <row r="20">
@@ -747,11 +747,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.3448702419906</v>
+        <v>27.40154399453787</v>
       </c>
     </row>
     <row r="21">
@@ -763,11 +763,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33.2225183412214</v>
+        <v>28.5946892676984</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +775,15 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.38893772607745</v>
+        <v>21.58891702561983</v>
       </c>
     </row>
     <row r="23">
@@ -791,15 +791,15 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.27963523990991</v>
+        <v>28.86453455410322</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.77675459896242</v>
+        <v>28.29999056640506</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.11465502098826</v>
+        <v>25.2447870926051</v>
       </c>
     </row>
     <row r="26">
@@ -843,11 +843,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.50206444341843</v>
+        <v>27.24528641936691</v>
       </c>
     </row>
     <row r="27">
@@ -855,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.37531577163837</v>
+        <v>33.7056274889384</v>
       </c>
     </row>
     <row r="28">
@@ -871,15 +871,15 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.16934054869541</v>
+        <v>25.26760610870734</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.95759471517161</v>
+        <v>25.24420071282895</v>
       </c>
     </row>
     <row r="30">
@@ -903,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.19681389640762</v>
+        <v>32.49589686047381</v>
       </c>
     </row>
     <row r="31">
@@ -919,7 +919,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.55175658744723</v>
+        <v>21.17520446177121</v>
       </c>
     </row>
     <row r="32">
@@ -935,7 +935,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.80216299552592</v>
+        <v>27.28006027081649</v>
       </c>
     </row>
     <row r="33">
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>25.43039423062309</v>
+        <v>32.52677676539652</v>
       </c>
     </row>
     <row r="34">
@@ -967,15 +967,15 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>26.95120966017848</v>
+        <v>25.89036176615701</v>
       </c>
     </row>
     <row r="35">
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.53376332056542</v>
+        <v>25.12782470659361</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +999,15 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27.55401687711058</v>
+        <v>32.94747197654592</v>
       </c>
     </row>
     <row r="37">
@@ -1015,15 +1015,15 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.24281075496421</v>
+        <v>21.12863585765485</v>
       </c>
     </row>
     <row r="38">
@@ -1031,15 +1031,15 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25.83713338370016</v>
+        <v>27.0346954821531</v>
       </c>
     </row>
     <row r="39">
@@ -1047,15 +1047,15 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.95442335124419</v>
+        <v>33.01986392290021</v>
       </c>
     </row>
     <row r="40">
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.90314251964986</v>
+        <v>26.18488351398837</v>
       </c>
     </row>
     <row r="41">
@@ -1079,15 +1079,15 @@
         <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27.75007023094759</v>
+        <v>25.12072344766357</v>
       </c>
     </row>
     <row r="42">
@@ -1095,15 +1095,15 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.50190452685903</v>
+        <v>32.29563412837216</v>
       </c>
     </row>
     <row r="43">
@@ -1111,15 +1111,15 @@
         <v>3</v>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.51954842750967</v>
+        <v>21.3477211455508</v>
       </c>
     </row>
     <row r="44">
@@ -1127,15 +1127,15 @@
         <v>3</v>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.95326488412278</v>
+        <v>27.28150935994877</v>
       </c>
     </row>
     <row r="45">
@@ -1143,15 +1143,15 @@
         <v>3</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>35.95945792221276</v>
+        <v>33.50783711354018</v>
       </c>
     </row>
     <row r="46">
@@ -1159,15 +1159,15 @@
         <v>3</v>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>33.06357040009085</v>
+        <v>25.765196574081</v>
       </c>
     </row>
     <row r="47">
@@ -1175,15 +1175,15 @@
         <v>3</v>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30.36554705572646</v>
+        <v>24.95636800921303</v>
       </c>
     </row>
     <row r="48">
@@ -1191,15 +1191,15 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25.98280136650622</v>
+        <v>32.34032649337934</v>
       </c>
     </row>
     <row r="49">
@@ -1207,15 +1207,15 @@
         <v>3</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27.812226840564</v>
+        <v>20.92787807291019</v>
       </c>
     </row>
     <row r="50">
@@ -1223,15 +1223,15 @@
         <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>36.97349000947206</v>
+        <v>29.69337291948554</v>
       </c>
     </row>
     <row r="51">
@@ -1239,15 +1239,15 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33.01575901212499</v>
+        <v>22.57169482725498</v>
       </c>
     </row>
     <row r="52">
@@ -1255,15 +1255,15 @@
         <v>3</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30.40982745276809</v>
+        <v>20.82113903477397</v>
       </c>
     </row>
     <row r="53">
@@ -1271,15 +1271,15 @@
         <v>3</v>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.30145816786042</v>
+        <v>28.48423399192464</v>
       </c>
     </row>
     <row r="54">
@@ -1287,15 +1287,15 @@
         <v>3</v>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27.8419686594632</v>
+        <v>31.75943239763188</v>
       </c>
     </row>
     <row r="55">
@@ -1303,15 +1303,15 @@
         <v>3</v>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>37.18330414032852</v>
+        <v>26.55615718734973</v>
       </c>
     </row>
     <row r="56">
@@ -1319,15 +1319,15 @@
         <v>3</v>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>32.86245417026793</v>
+        <v>29.50424137872755</v>
       </c>
     </row>
     <row r="57">
@@ -1335,15 +1335,15 @@
         <v>3</v>
       </c>
       <c r="B57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30.64745538298842</v>
+        <v>22.3323075840303</v>
       </c>
     </row>
     <row r="58">
@@ -1351,15 +1351,15 @@
         <v>3</v>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>26.66556929469509</v>
+        <v>20.7864946041157</v>
       </c>
     </row>
     <row r="59">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.99850526904374</v>
+        <v>28.66657287497036</v>
       </c>
     </row>
     <row r="60">
@@ -1383,7 +1383,7 @@
         <v>3</v>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>36.3324502827707</v>
+        <v>32.82304206790047</v>
       </c>
     </row>
     <row r="61">
@@ -1399,7 +1399,7 @@
         <v>3</v>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>32.67313849184193</v>
+        <v>26.7148932948662</v>
       </c>
     </row>
     <row r="62">
@@ -1415,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.24366827842105</v>
+        <v>29.68195403293793</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         <v>3</v>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28.09594790456353</v>
+        <v>22.49616370095731</v>
       </c>
     </row>
     <row r="64">
@@ -1447,15 +1447,15 @@
         <v>3</v>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28.54226946053499</v>
+        <v>20.42058481452671</v>
       </c>
     </row>
     <row r="65">
@@ -1463,15 +1463,15 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>31.85709377597001</v>
+        <v>28.54364142778768</v>
       </c>
     </row>
     <row r="66">
@@ -1479,15 +1479,15 @@
         <v>3</v>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>22.17237120166851</v>
+        <v>32.23480314288297</v>
       </c>
     </row>
     <row r="67">
@@ -1495,15 +1495,15 @@
         <v>3</v>
       </c>
       <c r="B67" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30.24090949574455</v>
+        <v>27.32524198699894</v>
       </c>
     </row>
     <row r="68">
@@ -1511,15 +1511,15 @@
         <v>3</v>
       </c>
       <c r="B68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>28.12851126766015</v>
+        <v>29.54875460685063</v>
       </c>
     </row>
     <row r="69">
@@ -1527,15 +1527,15 @@
         <v>3</v>
       </c>
       <c r="B69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.76987581612416</v>
+        <v>22.58081077609426</v>
       </c>
     </row>
     <row r="70">
@@ -1543,15 +1543,15 @@
         <v>3</v>
       </c>
       <c r="B70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>32.13231772552221</v>
+        <v>20.81284739301471</v>
       </c>
     </row>
     <row r="71">
@@ -1559,15 +1559,15 @@
         <v>3</v>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>22.08737495181376</v>
+        <v>28.21753972262115</v>
       </c>
     </row>
     <row r="72">
@@ -1575,15 +1575,15 @@
         <v>3</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>30.56738978148566</v>
+        <v>32.58356467800201</v>
       </c>
     </row>
     <row r="73">
@@ -1591,15 +1591,15 @@
         <v>3</v>
       </c>
       <c r="B73" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>27.29237633519176</v>
+        <v>26.86886432652332</v>
       </c>
     </row>
     <row r="74">
@@ -1607,15 +1607,15 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.92785140297173</v>
+        <v>28.89136628262288</v>
       </c>
     </row>
     <row r="75">
@@ -1623,15 +1623,15 @@
         <v>3</v>
       </c>
       <c r="B75" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31.7961078073743</v>
+        <v>26.90994812286158</v>
       </c>
     </row>
     <row r="76">
@@ -1639,15 +1639,15 @@
         <v>3</v>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.25503232339022</v>
+        <v>20.51760233117985</v>
       </c>
     </row>
     <row r="77">
@@ -1655,15 +1655,15 @@
         <v>3</v>
       </c>
       <c r="B77" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>29.95060759165136</v>
+        <v>25.6201731212333</v>
       </c>
     </row>
     <row r="78">
@@ -1671,15 +1671,15 @@
         <v>3</v>
       </c>
       <c r="B78" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28.27863848340073</v>
+        <v>28.7860309413482</v>
       </c>
     </row>
     <row r="79">
@@ -1687,15 +1687,15 @@
         <v>3</v>
       </c>
       <c r="B79" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>28.03759095682877</v>
+        <v>30.78260273874037</v>
       </c>
     </row>
     <row r="80">
@@ -1703,15 +1703,15 @@
         <v>3</v>
       </c>
       <c r="B80" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>31.64194242593596</v>
+        <v>28.38068650770089</v>
       </c>
     </row>
     <row r="81">
@@ -1719,15 +1719,271 @@
         <v>3</v>
       </c>
       <c r="B81" t="n">
+        <v>14</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>27.00312068955846</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" t="n">
+        <v>14</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>20.25392745983839</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" t="n">
+        <v>14</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25.85361090628541</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" t="n">
+        <v>14</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>28.17431352871256</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="n">
+        <v>14</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>30.1434297540413</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" t="n">
+        <v>15</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>28.36011465848967</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" t="n">
+        <v>15</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>27.28552272085795</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" t="n">
+        <v>15</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>20.04773010566911</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" t="n">
+        <v>15</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>26.3871779333641</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" t="n">
+        <v>15</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>28.39393160443773</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>30.02576281094766</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="n">
         <v>16</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>28.89781159991372</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" t="n">
+        <v>16</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>26.82264494199301</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="n">
+        <v>16</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>20.27978794446976</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" t="n">
+        <v>16</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>26.32408989173987</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" t="n">
+        <v>16</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>28.15805278979747</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" t="n">
+        <v>16</v>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>22.43240852323821</v>
+      <c r="D97" t="n">
+        <v>30.17839352713929</v>
       </c>
     </row>
   </sheetData>
